--- a/manuscript/supplementary/Supplementary_Tables.xlsx
+++ b/manuscript/supplementary/Supplementary_Tables.xlsx
@@ -16078,7 +16078,7 @@
         </is>
       </c>
       <c r="V3" s="2" t="n">
-        <v>40</v>
+        <v>312</v>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         </is>
       </c>
       <c r="P6" s="2" t="n">
-        <v>-0.128</v>
+        <v>-0.13</v>
       </c>
       <c r="Q6" s="2" t="n">
         <v>0.203</v>
